--- a/registro_certificados_foro_2026.xlsx
+++ b/registro_certificados_foro_2026.xlsx
@@ -677,7 +677,11 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>jorgehhoyos@gmail.com</t>
+        </is>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>https://juannietoval.github.io/certificaci-n-II-foro/?id=FORO26-PON-003</t>
@@ -840,7 +844,11 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>erbetancourt@utp.edu.co</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>https://juannietoval.github.io/certificaci-n-II-foro/?id=FORO26-PON-006</t>
@@ -946,7 +954,11 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>ksantiana@bolivariano.edu.ec</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>https://juannietoval.github.io/certificaci-n-II-foro/?id=FORO26-PON-008</t>

--- a/registro_certificados_foro_2026.xlsx
+++ b/registro_certificados_foro_2026.xlsx
@@ -61,16 +61,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00E0E0E0"/>
+        <color rgb="00D0D7DE"/>
       </left>
       <right style="thin">
-        <color rgb="00E0E0E0"/>
+        <color rgb="00D0D7DE"/>
       </right>
       <top style="thin">
-        <color rgb="00E0E0E0"/>
+        <color rgb="00D0D7DE"/>
       </top>
       <bottom style="thin">
-        <color rgb="00E0E0E0"/>
+        <color rgb="00D0D7DE"/>
       </bottom>
     </border>
   </borders>
@@ -80,7 +80,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -453,23 +453,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
-    <col width="55" customWidth="1" min="10" max="10"/>
-    <col width="55" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Código Certificado</t>
@@ -512,7 +499,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Correo Electrónico</t>
+          <t>Correo Electrónica</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -567,7 +554,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>noheliay@gmail.com</t>
         </is>
@@ -624,7 +611,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>zahirasilano28@gmail.com</t>
         </is>
@@ -677,7 +664,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>jorgehhoyos@gmail.com</t>
         </is>
@@ -734,7 +721,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>fabian.zarta@uniminuto.edu</t>
         </is>
@@ -791,7 +778,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>fgalvez175@gmail.com</t>
         </is>
@@ -844,7 +831,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>erbetancourt@utp.edu.co</t>
         </is>
@@ -901,7 +888,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>profesorayeseniacenteno@gmail.com</t>
         </is>
@@ -954,7 +941,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>ksantiana@bolivariano.edu.ec</t>
         </is>
@@ -1007,7 +994,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>https://juannietoval.github.io/certificaci-n-II-foro/?id=FORO26-PON-009</t>
@@ -1056,7 +1043,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
           <t>https://juannietoval.github.io/certificaci-n-II-foro/?id=FORO26-PON-010</t>
@@ -1109,7 +1096,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>profe.reisner@gmail.com</t>
         </is>
@@ -1162,7 +1149,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
           <t>https://juannietoval.github.io/certificaci-n-II-foro/?id=FORO26-PON-012</t>
@@ -1171,6 +1158,63 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>certificados/ponentes/certificado - Dr. Benjamín Barón Velandia.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>FORO26-PON-013</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Leandro Ceballos Henao</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>C.C. 1.039.447.159</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Corporación Universitaria Minuto de Dios - UNIMINUTO</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Publicación científica para todas las personas: accesibilidad e inclusividad como criterios de calidad editorial</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Ética y buenas prácticas editoriales</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4 horas</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>tiflo.ceballos@gmail.com</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>https://juannietoval.github.io/certificaci-n-II-foro/?id=FORO26-PON-013</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>certificados/ponentes/certificado - Leandro Ceballos Henao.pdf</t>
         </is>
       </c>
     </row>
@@ -1185,22 +1229,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="54" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
-    <col width="55" customWidth="1" min="10" max="10"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Código Certificado</t>
@@ -1288,7 +1320,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>cymartinezr@correo.udistrital.edu.co</t>
         </is>
@@ -1340,7 +1372,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>ana.machado@udea.edu.co</t>
         </is>
@@ -1392,7 +1424,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>jlsanchez@ufpso.edu.co</t>
         </is>
@@ -1444,7 +1476,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>VDominguez@austral.edu.ar</t>
         </is>
@@ -1496,7 +1528,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>caro.hiparquia@gmail.com</t>
         </is>
@@ -1548,7 +1580,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>malejandra008@gmail.com</t>
         </is>
@@ -1600,7 +1632,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>juliafaganamosen2024@gmail.com</t>
         </is>
@@ -1652,7 +1684,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>pablo.martines@unac.edu.co</t>
         </is>
@@ -1704,7 +1736,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>eduardo.menjivar@udb.edu.sv</t>
         </is>
@@ -1756,7 +1788,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>carloslizcano1972@gmail.com</t>
         </is>
@@ -1808,7 +1840,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>profundidad@ufpso.edu.co</t>
         </is>
@@ -1860,7 +1892,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>juan.nieto2@utp.edu.co</t>
         </is>
@@ -1912,7 +1944,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>maria.tolentino@ugto.mx</t>
         </is>
@@ -1964,7 +1996,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>investigacioninhrr@gmail.com</t>
         </is>
@@ -2016,7 +2048,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>franciscorosendo31@rcastellanos.cdmx.gob.mx</t>
         </is>
@@ -2068,7 +2100,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>mariaesgonzalez@udec.cl</t>
         </is>
@@ -2120,7 +2152,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>dahiana.jimenez@ucr.ac.cr</t>
         </is>
@@ -2172,7 +2204,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>lperilla@unal.edu.co</t>
         </is>
@@ -2224,7 +2256,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>celinahernandezarmenta8@gmail.com</t>
         </is>
@@ -2276,7 +2308,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>milaislet.unefm@gmail.com</t>
         </is>
@@ -2328,7 +2360,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>gelis1969@gmail.com</t>
         </is>
@@ -2380,7 +2412,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>anagarcia210895@gmail.com</t>
         </is>
@@ -2432,7 +2464,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>5cinthyagutierrez@gmail.com</t>
         </is>
@@ -2484,7 +2516,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>oscar_chavez_1992@hotmail.com</t>
         </is>
@@ -2536,7 +2568,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>rcarosan@gmail.com</t>
         </is>
@@ -2588,7 +2620,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>texeiraalexandre@gmail.com</t>
         </is>
@@ -2640,7 +2672,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>xgarcia@umanizales.edu.co</t>
         </is>
@@ -2692,7 +2724,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>rcordova@urp.edu.pe</t>
         </is>
@@ -2744,7 +2776,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>CAMICORCHUELO@GMAIL.COM</t>
         </is>
@@ -2796,7 +2828,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>e.blancarte@ugto.mx</t>
         </is>
@@ -2848,7 +2880,7 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>paulina.pereda@uaq.edu.mx</t>
         </is>
@@ -2872,22 +2904,22 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Leandro Ceballos Henao</t>
+          <t>Edgar Zapata Vívenes</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>C.C. 1.039.447.159</t>
+          <t>DNI 0963250295</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Corporación Universitaria Minuto de Dios UNIMINUTO</t>
+          <t>Universidad Técnica de Manabí</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Medellín Colombia</t>
+          <t>Ecuador, Bahía de Caráquez</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -2900,9 +2932,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>tiflo.ceballos@gmail.com</t>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>edgar.zapata@utm.edu.ec</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -2912,7 +2944,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Leandro Ceballos Henao.pdf</t>
+          <t>certificados/asistentes/certificado - Edgar Zapata Vívenes.pdf</t>
         </is>
       </c>
     </row>
@@ -2924,22 +2956,22 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Edgar Zapata Vívenes</t>
+          <t>Karla Mavel Bolo Romero</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>DNI 0963250295</t>
+          <t>DNI 10627224</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Universidad Técnica de Manabí</t>
+          <t>Universidad Femenina del Sagrado Corazón</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Ecuador, Bahía de Caráquez</t>
+          <t>Perú - Lima</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -2952,9 +2984,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>edgar.zapata@utm.edu.ec</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>karlambr@gmail.com</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -2964,7 +2996,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Edgar Zapata Vívenes.pdf</t>
+          <t>certificados/asistentes/certificado - Karla Mavel Bolo Romero.pdf</t>
         </is>
       </c>
     </row>
@@ -2976,22 +3008,22 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Karla Mavel Bolo Romero</t>
+          <t>Sheyla Verónica Calderón de Rodríguez</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>DNI 10627224</t>
+          <t>C.E. 04-147-1857</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Universidad Femenina del Sagrado Corazón</t>
+          <t>Universidad Autónoma de Chiriquí.</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Perú - Lima</t>
+          <t>Panamá</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -3004,9 +3036,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>karlambr@gmail.com</t>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>sheyla.calderon@unachi.ac.pa</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -3016,7 +3048,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Karla Mavel Bolo Romero.pdf</t>
+          <t>certificados/asistentes/certificado - Sheyla Verónica Calderón de Rodríguez.pdf</t>
         </is>
       </c>
     </row>
@@ -3028,22 +3060,22 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Sheyla Verónica Calderón de Rodríguez</t>
+          <t>Nancy Isela Lopez Rodriguez</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>C.E. 04-147-1857</t>
+          <t>DNI 41984068</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Universidad Autónoma de Chiriquí.</t>
+          <t>Universidad Nacional de Trujillo</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Panamá</t>
+          <t>Perú / Trujillo</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -3056,9 +3088,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>sheyla.calderon@unachi.ac.pa</t>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>nlopez@unitru.edu.pe</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -3068,7 +3100,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Sheyla Verónica Calderón de Rodríguez.pdf</t>
+          <t>certificados/asistentes/certificado - Nancy Isela Lopez Rodriguez.pdf</t>
         </is>
       </c>
     </row>
@@ -3080,22 +3112,22 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Nancy Isela Lopez Rodriguez</t>
+          <t>Margarita Velasco Jiménez</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>DNI 41984068</t>
+          <t>DNI 50092398P</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Universidad Nacional de Trujillo</t>
+          <t>Revista Vivat Academia</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Perú / Trujillo</t>
+          <t>Madrid, España</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -3108,9 +3140,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>nlopez@unitru.edu.pe</t>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>contabilidad@seeci.net</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -3120,7 +3152,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Nancy Isela Lopez Rodriguez.pdf</t>
+          <t>certificados/asistentes/certificado - Margarita Velasco Jiménez.pdf</t>
         </is>
       </c>
     </row>
@@ -3132,22 +3164,22 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Margarita Velasco Jiménez</t>
+          <t>Leidy Marcela Osorio Manco</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>DNI 50092398P</t>
+          <t>C.C. 1.128.281.084</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Revista Vivat Academia</t>
+          <t>Universidad de Antioquia</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Madrid, España</t>
+          <t>Colombia - Medellín</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -3160,9 +3192,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>contabilidad@seeci.net</t>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>leidymarcelaosoriom@gmail.com</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -3172,7 +3204,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Margarita Velasco Jiménez.pdf</t>
+          <t>certificados/asistentes/certificado - Leidy Marcela Osorio Manco.pdf</t>
         </is>
       </c>
     </row>
@@ -3184,22 +3216,22 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Leidy Marcela Osorio Manco</t>
+          <t>María Guadalupe Rodríguez Oliva</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>C.C. 1.128.281.084</t>
+          <t>C.E. Roog741210</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Universidad de Antioquia</t>
+          <t>Universidad Autónoma de San Luis Potosi</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Colombia - Medellín</t>
+          <t>México</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -3212,9 +3244,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>leidymarcelaosoriom@gmail.com</t>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>maria.oliva@uaslp.mx</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -3224,7 +3256,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Leidy Marcela Osorio Manco.pdf</t>
+          <t>certificados/asistentes/certificado - María Guadalupe Rodríguez Oliva.pdf</t>
         </is>
       </c>
     </row>
@@ -3236,22 +3268,22 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>María Guadalupe Rodríguez Oliva</t>
+          <t>Corina Echavarría</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>C.E. Roog741210</t>
+          <t>DNI 22224881</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Universidad Autónoma de San Luis Potosi</t>
+          <t>Editora Revista Administración Pública y Sociedad, Instituto de Investigación y Formación en Administración Pública. Universidad Nacional de Córdoba.</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Córdoba, Argentina</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -3264,9 +3296,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>maria.oliva@uaslp.mx</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>cechavarria@unc.edu.ar</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -3276,7 +3308,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - María Guadalupe Rodríguez Oliva.pdf</t>
+          <t>certificados/asistentes/certificado - Corina Echavarría.pdf</t>
         </is>
       </c>
     </row>
@@ -3288,22 +3320,22 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Corina Echavarría</t>
+          <t>Analía Pérez Ruchel</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>DNI 22224881</t>
+          <t>DNI 40386523</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Editora Revista Administración Pública y Sociedad, Instituto de Investigación y Formación en Administración Pública. Universidad Nacional de Córdoba.</t>
+          <t>Facultad de Veterinaria - UDELAR</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Córdoba, Argentina</t>
+          <t>Uruguay, Montevideo</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -3316,9 +3348,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>cechavarria@unc.edu.ar</t>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>analia.perez@fvet.edu.uy</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -3328,7 +3360,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Corina Echavarría.pdf</t>
+          <t>certificados/asistentes/certificado - Analía Pérez Ruchel.pdf</t>
         </is>
       </c>
     </row>
@@ -3340,22 +3372,22 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Analía Pérez Ruchel</t>
+          <t>Camila José Vásquez Avila</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>DNI 40386523</t>
+          <t>C.E. 0301988994</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Facultad de Veterinaria - UDELAR</t>
+          <t>Universidad Católica de Cuenca</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Uruguay, Montevideo</t>
+          <t>Cuenca, Ecuador</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -3368,9 +3400,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>analia.perez@fvet.edu.uy</t>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>camila.vasquez@ucacue.edu.ec</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -3380,7 +3412,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Analía Pérez Ruchel.pdf</t>
+          <t>certificados/asistentes/certificado - Camila José Vásquez Avila.pdf</t>
         </is>
       </c>
     </row>
@@ -3392,22 +3424,22 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Camila José Vásquez Avila</t>
+          <t>Moncerrath Arenas</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>C.E. 0301988994</t>
+          <t>INE ARRYAL8602289M700</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Universidad Católica de Cuenca</t>
+          <t>Ceu</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Cuenca, Ecuador</t>
+          <t>México</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -3420,9 +3452,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>camila.vasquez@ucacue.edu.ec</t>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>moncerratharenas@gmail.com</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -3432,7 +3464,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Camila José Vásquez Avila.pdf</t>
+          <t>certificados/asistentes/certificado - Moncerrath Arenas.pdf</t>
         </is>
       </c>
     </row>
@@ -3444,22 +3476,22 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Moncerrath Arenas</t>
+          <t>Julian Díaz</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>INE ARRYAL8602289M700</t>
+          <t>C.C. 15.992.162</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Ceu</t>
+          <t>Universidad Bicentenaria de Aragua</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Venezuela, Maracay</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -3472,9 +3504,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>moncerratharenas@gmail.com</t>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>jadt08@gmail.com</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -3484,7 +3516,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Moncerrath Arenas.pdf</t>
+          <t>certificados/asistentes/certificado - Julian Díaz.pdf</t>
         </is>
       </c>
     </row>
@@ -3496,22 +3528,22 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Julian Díaz</t>
+          <t>Fátima Mayerli Fuentes</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>C.C. 15.992.162</t>
+          <t>DUI 06909511-9</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Universidad Bicentenaria de Aragua</t>
+          <t>Instituto Nacional de Puerto El Triunfo</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Venezuela, Maracay</t>
+          <t>El Salvador, Puerto El Triunfo</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -3524,9 +3556,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>jadt08@gmail.com</t>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>mayerli.fmf33@gmail.com</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -3536,7 +3568,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Julian Díaz.pdf</t>
+          <t>certificados/asistentes/certificado - Fátima Mayerli Fuentes.pdf</t>
         </is>
       </c>
     </row>
@@ -3548,22 +3580,22 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Fátima Mayerli Fuentes</t>
+          <t>Jorgelina Passo</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>DUI 06909511-9</t>
+          <t>DNI 26618542</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Instituto Nacional de Puerto El Triunfo</t>
+          <t>Universidad de Buenos Aires</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>El Salvador, Puerto El Triunfo</t>
+          <t>Argentina, Buenos Aires</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -3576,9 +3608,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>mayerli.fmf33@gmail.com</t>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>jorpasso@gmail.com</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -3588,7 +3620,7 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Fátima Mayerli Fuentes.pdf</t>
+          <t>certificados/asistentes/certificado - Jorgelina Passo.pdf</t>
         </is>
       </c>
     </row>
@@ -3600,22 +3632,22 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Jorgelina Passo</t>
+          <t>Dorelys Domenyca Morales Chirinos</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>DNI 26618542</t>
+          <t>C.E. 13107853</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Universidad de Buenos Aires</t>
+          <t>UPEL</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Argentina, Buenos Aires</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -3628,9 +3660,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>jorpasso@gmail.com</t>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>dorelysmorales2@gmail.com</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -3640,7 +3672,7 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Jorgelina Passo.pdf</t>
+          <t>certificados/asistentes/certificado - Dorelys Domenyca Morales Chirinos.pdf</t>
         </is>
       </c>
     </row>
@@ -3652,22 +3684,22 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Dorelys Domenyca Morales Chirinos</t>
+          <t>Doris Cristina Vanegas González</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>C.E. 13107853</t>
+          <t>C.C. 1.037.640.322</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>UPEL</t>
+          <t>Fundación Universitaria Colombo Internacional - Unicolombo</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Cartagena de Indias, Colombia</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -3680,9 +3712,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>dorelysmorales2@gmail.com</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>coordbiblioteca@unicolombo.edu.co</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
@@ -3692,7 +3724,7 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Dorelys Domenyca Morales Chirinos.pdf</t>
+          <t>certificados/asistentes/certificado - Doris Cristina Vanegas González.pdf</t>
         </is>
       </c>
     </row>
@@ -3704,22 +3736,22 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Doris Cristina Vanegas González</t>
+          <t>Fabiola Núñez Pastrana</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>C.C. 1.037.640.322</t>
+          <t>INE NZPSFB77062609M000</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Fundación Universitaria Colombo Internacional - Unicolombo</t>
+          <t>Universidad Michoacana de San Nicolás de Hidalgo</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Cartagena de Indias, Colombia</t>
+          <t>México, Morelia</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -3732,9 +3764,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>coordbiblioteca@unicolombo.edu.co</t>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>fabiola.pastrana@umich.mx</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -3744,7 +3776,7 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Doris Cristina Vanegas González.pdf</t>
+          <t>certificados/asistentes/certificado - Fabiola Núñez Pastrana.pdf</t>
         </is>
       </c>
     </row>
@@ -3756,22 +3788,22 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Fabiola Núñez Pastrana</t>
+          <t>Rodolfo Bolaños</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>INE NZPSFB77062609M000</t>
+          <t>C.C. 94.524.701</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Universidad Michoacana de San Nicolás de Hidalgo</t>
+          <t>Corporación Universitaria Minuto de Dios</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>México, Morelia</t>
+          <t>Colombia - Cali</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -3784,9 +3816,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>fabiola.pastrana@umich.mx</t>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>rodolfobolanosbarrera78@gmail.com</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -3796,7 +3828,7 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Fabiola Núñez Pastrana.pdf</t>
+          <t>certificados/asistentes/certificado - Rodolfo Bolaños.pdf</t>
         </is>
       </c>
     </row>
@@ -3808,22 +3840,22 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Rodolfo Bolaños</t>
+          <t>María de la Luz Escamilla Moya</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>C.C. 94.524.701</t>
+          <t>D.I. EAML670512MDFSYZ03</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Corporación Universitaria Minuto de Dios</t>
+          <t>Instituto de Ciencias Nucleares,UNAM</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Colombia - Cali</t>
+          <t>México, Ciudad de México</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -3836,9 +3868,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>rodolfobolanosbarrera78@gmail.com</t>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>maluz.escamilla@gmail.com</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -3848,7 +3880,7 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Rodolfo Bolaños.pdf</t>
+          <t>certificados/asistentes/certificado - María de la Luz Escamilla Moya.pdf</t>
         </is>
       </c>
     </row>
@@ -3860,22 +3892,22 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>María de la Luz Escamilla Moya</t>
+          <t>Mayra Itzel Huerta Baltazar</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>D.I. EAML670512MDFSYZ03</t>
+          <t>DNI 2603903584</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Instituto de Ciencias Nucleares,UNAM</t>
+          <t>Universidad Michoacana de San Nicolás de Hidalgo</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>México, Ciudad de México</t>
+          <t>Morelia, Michoacán</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -3888,9 +3920,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>maluz.escamilla@gmail.com</t>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>mayra.huerta@umich.mx</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -3900,7 +3932,7 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - María de la Luz Escamilla Moya.pdf</t>
+          <t>certificados/asistentes/certificado - Mayra Itzel Huerta Baltazar.pdf</t>
         </is>
       </c>
     </row>
@@ -3912,22 +3944,22 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Mayra Itzel Huerta Baltazar</t>
+          <t>Belkis Elizabeth Osorio Acosta</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>DNI 2603903584</t>
+          <t>C.E. 60367544L</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Universidad Michoacana de San Nicolás de Hidalgo</t>
+          <t>Corporación Politécnico del Norte-POLINORTE</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Morelia, Michoacán</t>
+          <t>Colombia-Sincelejo</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -3940,9 +3972,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>mayra.huerta@umich.mx</t>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>belkys.osorio@gmail.com</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -3952,7 +3984,7 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Mayra Itzel Huerta Baltazar.pdf</t>
+          <t>certificados/asistentes/certificado - Belkis Elizabeth Osorio Acosta.pdf</t>
         </is>
       </c>
     </row>
@@ -3964,22 +3996,22 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Belkis Elizabeth Osorio Acosta</t>
+          <t>Katty Cordero Fuentes</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>C.E. 60367544L</t>
+          <t>DNI 111340258</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Corporación Politécnico del Norte-POLINORTE</t>
+          <t>Universidad de Costa Rica</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Colombia-Sincelejo</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -3992,9 +4024,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>belkys.osorio@gmail.com</t>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>reflexiones.fcs@ucr.ac.cr</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -4004,7 +4036,7 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Belkis Elizabeth Osorio Acosta.pdf</t>
+          <t>certificados/asistentes/certificado - Katty Cordero Fuentes.pdf</t>
         </is>
       </c>
     </row>
@@ -4016,22 +4048,22 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Katty Cordero Fuentes</t>
+          <t>Dr. Juan Carlos Abreu y Abreu</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>DNI 111340258</t>
+          <t>Pasaporte N00465298</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Universidad de Costa Rica</t>
+          <t>Universidad Anáhuac México</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Huixquilucan, Estado de México. México</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -4044,9 +4076,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>reflexiones.fcs@ucr.ac.cr</t>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>juan.abreuya@anahuac.mx</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -4056,7 +4088,7 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Katty Cordero Fuentes.pdf</t>
+          <t>certificados/asistentes/certificado - Dr. Juan Carlos Abreu y Abreu.pdf</t>
         </is>
       </c>
     </row>
@@ -4068,22 +4100,22 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Dr. Juan Carlos Abreu y Abreu</t>
+          <t>Eva Luna Contreras</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Pasaporte N00465298</t>
+          <t>C.C. 1.140.886.894</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Universidad Anáhuac México</t>
+          <t>Corporación Universitaria Americana</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Huixquilucan, Estado de México. México</t>
+          <t>Colombia / Barranquilla</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -4096,9 +4128,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>juan.abreuya@anahuac.mx</t>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>econtreras@americana.edu.co</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -4108,7 +4140,7 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Dr. Juan Carlos Abreu y Abreu.pdf</t>
+          <t>certificados/asistentes/certificado - Eva Luna Contreras.pdf</t>
         </is>
       </c>
     </row>
@@ -4120,22 +4152,22 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Eva Luna Contreras</t>
+          <t>Darlington Smith Galvan Añez</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>C.C. 1.140.886.894</t>
+          <t>C.C. 1.004.805.265</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Corporación Universitaria Americana</t>
+          <t>Universidad Francisco de Paula Santander</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Colombia / Barranquilla</t>
+          <t>Colombia - Cúcuta</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -4148,9 +4180,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>econtreras@americana.edu.co</t>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>revistavisioninternacional@ufps.edu.co</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -4160,7 +4192,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Eva Luna Contreras.pdf</t>
+          <t>certificados/asistentes/certificado - Darlington Smith Galvan Añez.pdf</t>
         </is>
       </c>
     </row>
@@ -4172,22 +4204,22 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Darlington Smith Galvan Añez</t>
+          <t>Alán Armando Cortés López</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>C.C. 1.004.805.265</t>
+          <t>INE 2035068950939</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Universidad Francisco de Paula Santander</t>
+          <t>Dirección de Educación Normal</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Colombia - Cúcuta</t>
+          <t>Xalapa, Veracruz, México</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -4200,9 +4232,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>revistavisioninternacional@ufps.edu.co</t>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>eduscientia.divulgacion@gmail.com</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
@@ -4212,7 +4244,7 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Darlington Smith Galvan Añez.pdf</t>
+          <t>certificados/asistentes/certificado - Alán Armando Cortés López.pdf</t>
         </is>
       </c>
     </row>
@@ -4224,22 +4256,22 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Alán Armando Cortés López</t>
+          <t>Itzel Miranda López</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>INE 2035068950939</t>
+          <t>INE 2156919108</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Dirección de Educación Normal</t>
+          <t>Universidad Autónoma de Occidente</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Xalapa, Veracruz, México</t>
+          <t>México Culiacán</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -4252,9 +4284,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>eduscientia.divulgacion@gmail.com</t>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>itzel.miranda.lopez@gmail.com</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -4264,7 +4296,7 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Alán Armando Cortés López.pdf</t>
+          <t>certificados/asistentes/certificado - Itzel Miranda López.pdf</t>
         </is>
       </c>
     </row>
@@ -4276,22 +4308,22 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Itzel Miranda López</t>
+          <t>Diana Fiorela Sanchez Velazco</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>INE 2156919108</t>
+          <t>DNI 73044736</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Universidad Autónoma de Occidente</t>
+          <t>Revista del Hospital Nacional Almanzor Aguinaga Asenjo</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>México Culiacán</t>
+          <t>Perú, Lima</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -4304,9 +4336,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>itzel.miranda.lopez@gmail.com</t>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>diana.rcmhnaaa@gmail.com</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -4316,7 +4348,7 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Itzel Miranda López.pdf</t>
+          <t>certificados/asistentes/certificado - Diana Fiorela Sanchez Velazco.pdf</t>
         </is>
       </c>
     </row>
@@ -4328,22 +4360,22 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Diana Fiorela Sanchez Velazco</t>
+          <t>Frank Isaac Berrocal Aréstegui</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>DNI 73044736</t>
+          <t>DNI 42531679</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Revista del Hospital Nacional Almanzor Aguinaga Asenjo</t>
+          <t>Universidad Nacional de San Cristóbal de Huamanga</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Perú, Lima</t>
+          <t>Perú, Ayacucho</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -4356,9 +4388,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>diana.rcmhnaaa@gmail.com</t>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>frank.berrocal.40@unsch.edu.pe</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -4368,7 +4400,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Diana Fiorela Sanchez Velazco.pdf</t>
+          <t>certificados/asistentes/certificado - Frank Isaac Berrocal Aréstegui.pdf</t>
         </is>
       </c>
     </row>
@@ -4380,22 +4412,22 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Frank Isaac Berrocal Aréstegui</t>
+          <t>Ricardo Aram Del Castillo Torres</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>DNI 42531679</t>
+          <t>INE 1690573856</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Universidad Nacional de San Cristóbal de Huamanga</t>
+          <t>UANL</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Perú, Ayacucho</t>
+          <t>México, Monterrey</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -4408,9 +4440,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>frank.berrocal.40@unsch.edu.pe</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>ricardo.delcastillotrs@uanl.edu.mx</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -4420,7 +4452,7 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Frank Isaac Berrocal Aréstegui.pdf</t>
+          <t>certificados/asistentes/certificado - Ricardo Aram Del Castillo Torres.pdf</t>
         </is>
       </c>
     </row>
@@ -4432,22 +4464,22 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Ricardo Aram Del Castillo Torres</t>
+          <t>Verónica Rivera de la Rosa</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>INE 1690573856</t>
+          <t>Pasaporte N10138128</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>UANL</t>
+          <t>Universidad Autónoma de Nuevo León</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>México, Monterrey</t>
+          <t>Monterrey, México</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -4460,9 +4492,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>ricardo.delcastillotrs@uanl.edu.mx</t>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>veronica.riveradl@gmail.com</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -4472,7 +4504,7 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Ricardo Aram Del Castillo Torres.pdf</t>
+          <t>certificados/asistentes/certificado - Verónica Rivera de la Rosa.pdf</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4516,12 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Verónica Rivera de la Rosa</t>
+          <t>Pablo García González</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Pasaporte N10138128</t>
+          <t>INE GRGNPB77121619H400</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -4499,7 +4531,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Monterrey, México</t>
+          <t>México, Monterrey</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -4512,9 +4544,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>veronica.riveradl@gmail.com</t>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>pablo.offset@gmail.com</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -4524,7 +4556,7 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Verónica Rivera de la Rosa.pdf</t>
+          <t>certificados/asistentes/certificado - Pablo García González.pdf</t>
         </is>
       </c>
     </row>
@@ -4536,22 +4568,22 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Pablo García González</t>
+          <t>Andrea Wilches Torres</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>INE GRGNPB77121619H400</t>
+          <t>C.C. 40.046.426</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Universidad Autónoma de Nuevo León</t>
+          <t>Universidad de Boyacá</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>México, Monterrey</t>
+          <t>Colombia, Tunja (Boyacá)</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -4564,9 +4596,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>pablo.offset@gmail.com</t>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>andreawilches@uniboyaca.edu.co</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -4576,7 +4608,7 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Pablo García González.pdf</t>
+          <t>certificados/asistentes/certificado - Andrea Wilches Torres.pdf</t>
         </is>
       </c>
     </row>
@@ -4588,22 +4620,22 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Andrea Wilches Torres</t>
+          <t>Bertha Jacqueline Contla Ramírez</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>C.C. 40.046.426</t>
+          <t>INE 0069010511866</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Universidad de Boyacá</t>
+          <t>Universidad de Colima</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Colombia, Tunja (Boyacá)</t>
+          <t>México, Colima</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
@@ -4616,9 +4648,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>andreawilches@uniboyaca.edu.co</t>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>contla@ucol.mx</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
@@ -4628,7 +4660,7 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Andrea Wilches Torres.pdf</t>
+          <t>certificados/asistentes/certificado - Bertha Jacqueline Contla Ramírez.pdf</t>
         </is>
       </c>
     </row>
@@ -4640,22 +4672,22 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Bertha Jacqueline Contla Ramírez</t>
+          <t>José Luis Aguilar Martínez</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>INE 0069010511866</t>
+          <t>Pasaporte N29874207</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Universidad de Colima</t>
+          <t>Universidad Autónoma de Guerrero</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>México, Colima</t>
+          <t>México, estado de Guerrero, Chilpancingo</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -4668,9 +4700,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>contla@ucol.mx</t>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>profesorluisaguilar@gmail.com</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -4680,7 +4712,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Bertha Jacqueline Contla Ramírez.pdf</t>
+          <t>certificados/asistentes/certificado - José Luis Aguilar Martínez.pdf</t>
         </is>
       </c>
     </row>
@@ -4692,22 +4724,22 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>José Luis Aguilar Martínez</t>
+          <t>Giovana Iris Hurtado Magán</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Pasaporte N29874207</t>
+          <t>DNI 09646377</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Universidad Autónoma de Guerrero</t>
+          <t>Universidad ESAN</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>México, estado de Guerrero, Chilpancingo</t>
+          <t>Lima, Perú</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -4720,9 +4752,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>profesorluisaguilar@gmail.com</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>ghurtado@esan.edu.pe</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -4732,7 +4764,7 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - José Luis Aguilar Martínez.pdf</t>
+          <t>certificados/asistentes/certificado - Giovana Iris Hurtado Magán.pdf</t>
         </is>
       </c>
     </row>
@@ -4744,22 +4776,22 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Giovana Iris Hurtado Magán</t>
+          <t>Montserrat García Guerrero</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>DNI 09646377</t>
+          <t>Pasaporte G1324752</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Universidad ESAN</t>
+          <t>Universidad Autónoma de Zacatecas</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Lima, Perú</t>
+          <t>Zacatecas Zacatecas</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -4772,9 +4804,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>ghurtado@esan.edu.pe</t>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>montsegarcia@uaz.edu.mx</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -4784,7 +4816,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Giovana Iris Hurtado Magán.pdf</t>
+          <t>certificados/asistentes/certificado - Montserrat García Guerrero.pdf</t>
         </is>
       </c>
     </row>
@@ -4796,22 +4828,22 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Montserrat García Guerrero</t>
+          <t>Ana Francisca Gonzalez Pedraza</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Pasaporte G1324752</t>
+          <t>C.C. 1.127.654.910</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Universidad Autónoma de Zacatecas</t>
+          <t>Universidad de Pamplona</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Zacatecas Zacatecas</t>
+          <t>Colombia, Pamplona</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
@@ -4824,9 +4856,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>montsegarcia@uaz.edu.mx</t>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>ana.gonzalez2@unipamplona.edu.co</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -4836,7 +4868,7 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Montserrat García Guerrero.pdf</t>
+          <t>certificados/asistentes/certificado - Ana Francisca Gonzalez Pedraza.pdf</t>
         </is>
       </c>
     </row>
@@ -4848,22 +4880,22 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Ana Francisca Gonzalez Pedraza</t>
+          <t>Antonia Sampaio</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>C.C. 1.127.654.910</t>
+          <t>C.E. 98010009710</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Universidad de Pamplona</t>
+          <t>Universidade Federal do Ceará</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Colombia, Pamplona</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -4876,9 +4908,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>ana.gonzalez2@unipamplona.edu.co</t>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>rene@ufc.br</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -4888,7 +4920,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Ana Francisca Gonzalez Pedraza.pdf</t>
+          <t>certificados/asistentes/certificado - Antonia Sampaio.pdf</t>
         </is>
       </c>
     </row>
@@ -4900,22 +4932,22 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Antonia Sampaio</t>
+          <t>Myriam Patricia Benitez Gonzalez</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>C.E. 98010009710</t>
+          <t>DNI 3428799</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Universidade Federal do Ceará</t>
+          <t>Universidad Privada del Este - Cede central</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Paraguay - Ciudad del Este</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
@@ -4928,9 +4960,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>rene@ufc.br</t>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>pattybenitez37@gmail.com</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -4940,7 +4972,7 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Antonia Sampaio.pdf</t>
+          <t>certificados/asistentes/certificado - Myriam Patricia Benitez Gonzalez.pdf</t>
         </is>
       </c>
     </row>
@@ -4952,22 +4984,22 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Myriam Patricia Benitez Gonzalez</t>
+          <t>Laura Nelly Rodriguez Cantu</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>DNI 3428799</t>
+          <t>INE 2036226630</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Universidad Privada del Este - Cede central</t>
+          <t>Universidad Michoacana de San Nicolás de  Hidalgo</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Paraguay - Ciudad del Este</t>
+          <t>México, Morelia</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -4980,9 +5012,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>pattybenitez37@gmail.com</t>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>nelly.rodriguez@umich.mx</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -4992,7 +5024,7 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Myriam Patricia Benitez Gonzalez.pdf</t>
+          <t>certificados/asistentes/certificado - Laura Nelly Rodriguez Cantu.pdf</t>
         </is>
       </c>
     </row>
@@ -5004,22 +5036,22 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Laura Nelly Rodriguez Cantu</t>
+          <t>Cristina Segundo Alvarado</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>INE 2036226630</t>
+          <t>D.I. SEAC840907MDFGLR</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Universidad Michoacana de San Nicolás de  Hidalgo</t>
+          <t>REVISTA MEXICANA DE ENFERMERÍA</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>México, Morelia</t>
+          <t>CIUDAD DE MÉXICO, MÉXICO</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
@@ -5032,9 +5064,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>nelly.rodriguez@umich.mx</t>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>cristina.segundoa@incmnsz.mx</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -5044,7 +5076,7 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Laura Nelly Rodriguez Cantu.pdf</t>
+          <t>certificados/asistentes/certificado - Cristina Segundo Alvarado.pdf</t>
         </is>
       </c>
     </row>
@@ -5056,22 +5088,22 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Cristina Segundo Alvarado</t>
+          <t>Araceli Martinez Cruz</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>D.I. SEAC840907MDFGLR</t>
+          <t>D.I. MACA000830MDFRRRA1</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>REVISTA MEXICANA DE ENFERMERÍA</t>
+          <t>Universidad Autonoma del Estado de México</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>CIUDAD DE MÉXICO, MÉXICO</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -5084,9 +5116,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>cristina.segundoa@incmnsz.mx</t>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>araceli.martinez@profesor.uicm.edu.mx</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -5096,7 +5128,7 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Cristina Segundo Alvarado.pdf</t>
+          <t>certificados/asistentes/certificado - Araceli Martinez Cruz.pdf</t>
         </is>
       </c>
     </row>
@@ -5108,22 +5140,22 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Araceli Martinez Cruz</t>
+          <t>Marcelina Soydeth Jiménez Ávila</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>D.I. MACA000830MDFRRRA1</t>
+          <t>INE 0146121978589</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Universidad Autonoma del Estado de México</t>
+          <t>Universidad de Colima</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Colima, México</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -5136,9 +5168,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>araceli.martinez@profesor.uicm.edu.mx</t>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>mjimenez42@ucol.mx</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -5148,7 +5180,7 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Araceli Martinez Cruz.pdf</t>
+          <t>certificados/asistentes/certificado - Marcelina Soydeth Jiménez Ávila.pdf</t>
         </is>
       </c>
     </row>
@@ -5160,22 +5192,22 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Marcelina Soydeth Jiménez Ávila</t>
+          <t>Thailing Núñez Betancourt</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>INE 0146121978589</t>
+          <t>Pasaporte L064216</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Universidad de Colima</t>
+          <t>UNIVERSIDAD INTERNACIONAL CUBA-MEXICO</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Colima, México</t>
+          <t>TEXCOCO DE MORA.MEXICO</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -5188,9 +5220,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>mjimenez42@ucol.mx</t>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>revistahorizontesuicm@gmail.com</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -5200,7 +5232,7 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Marcelina Soydeth Jiménez Ávila.pdf</t>
+          <t>certificados/asistentes/certificado - Thailing Núñez Betancourt.pdf</t>
         </is>
       </c>
     </row>
@@ -5212,22 +5244,22 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Thailing Núñez Betancourt</t>
+          <t>Alba Brenda Daniel Guerrero</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Pasaporte L064216</t>
+          <t>D.I. DAGA8701145X0</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD INTERNACIONAL CUBA-MEXICO</t>
+          <t>Universidad Nacional Autónoma de México</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>TEXCOCO DE MORA.MEXICO</t>
+          <t>México</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -5240,9 +5272,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>revistahorizontesuicm@gmail.com</t>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>abren.dague@facmed.unam.mx</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -5252,7 +5284,7 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Thailing Núñez Betancourt.pdf</t>
+          <t>certificados/asistentes/certificado - Alba Brenda Daniel Guerrero.pdf</t>
         </is>
       </c>
     </row>
@@ -5264,22 +5296,22 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Alba Brenda Daniel Guerrero</t>
+          <t>Pascual Alberto Moreno Florez</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>D.I. DAGA8701145X0</t>
+          <t>C.I. 12228872</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Universidad Nacional Autónoma de México</t>
+          <t>Universidad de Los Andes-Táchira</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Venezuela, San Cristóbal</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -5292,9 +5324,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>abren.dague@facmed.unam.mx</t>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>pascualalbertomf@gmail.com</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -5304,7 +5336,7 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Alba Brenda Daniel Guerrero.pdf</t>
+          <t>certificados/asistentes/certificado - Pascual Alberto Moreno Florez.pdf</t>
         </is>
       </c>
     </row>
@@ -5316,22 +5348,22 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Pascual Alberto Moreno Florez</t>
+          <t>Erick López León</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>C.I. 12228872</t>
+          <t>Pasaporte N150053810</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Universidad de Los Andes-Táchira</t>
+          <t>Universidad Nacional Autónoma de México</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Venezuela, San Cristóbal</t>
+          <t>Ciudad de México México</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -5344,9 +5376,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>pascualalbertomf@gmail.com</t>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>lole.erick@gmail.com</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
@@ -5356,7 +5388,7 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Pascual Alberto Moreno Florez.pdf</t>
+          <t>certificados/asistentes/certificado - Erick López León.pdf</t>
         </is>
       </c>
     </row>
@@ -5368,22 +5400,22 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Erick López León</t>
+          <t>Martín Emmanuel Páez Alejo</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Pasaporte N150053810</t>
+          <t>INE PZALMR01010319H700</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Universidad Nacional Autónoma de México</t>
+          <t>Facultad de Trabajo Social y Desarrollo Humano</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Ciudad de México México</t>
+          <t>México, Nuevo León, Guadalupe.</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -5396,9 +5428,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>lole.erick@gmail.com</t>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>paezalejom@gmail.com</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -5408,7 +5440,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Erick López León.pdf</t>
+          <t>certificados/asistentes/certificado - Martín Emmanuel Páez Alejo.pdf</t>
         </is>
       </c>
     </row>
@@ -5420,22 +5452,18 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Martín Emmanuel Páez Alejo</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>INE PZALMR01010319H700</t>
-        </is>
-      </c>
+          <t>Elisa Gaytán Favela</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr"/>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Facultad de Trabajo Social y Desarrollo Humano</t>
+          <t>Universidad Autónoma de Nuevo León</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>México, Nuevo León, Guadalupe.</t>
+          <t>San Nicolás de los Garza, Nuevo León, México</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
@@ -5448,9 +5476,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>paezalejom@gmail.com</t>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>gurisagaytan@yahoo.com</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
@@ -5460,7 +5488,7 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Martín Emmanuel Páez Alejo.pdf</t>
+          <t>certificados/asistentes/certificado - Elisa Gaytán Favela.pdf</t>
         </is>
       </c>
     </row>
@@ -5472,18 +5500,22 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Elisa Gaytán Favela</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr"/>
+          <t>Angie Vanessa Burbano Erazo</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>C.C. 1.086.019.197</t>
+        </is>
+      </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Universidad Autónoma de Nuevo León</t>
+          <t>Universidad de Nariño</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>San Nicolás de los Garza, Nuevo León, México</t>
+          <t>Colombia - Pasto</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -5496,9 +5528,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>gurisagaytan@yahoo.com</t>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>revistatendencias@udenar.edu.co</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
@@ -5508,7 +5540,7 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Elisa Gaytán Favela.pdf</t>
+          <t>certificados/asistentes/certificado - Angie Vanessa Burbano Erazo.pdf</t>
         </is>
       </c>
     </row>
@@ -5520,22 +5552,22 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Angie Vanessa Burbano Erazo</t>
+          <t>Marco Antonio Cruz Chávez</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>C.C. 1.086.019.197</t>
+          <t>INE IDMEX2839443344</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Universidad de Nariño</t>
+          <t>UNIVERSIDAD AUTÓNOMA DEL ESTADO DE MORELOS</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Colombia - Pasto</t>
+          <t>CUERNAVACA, MORELOS, MÉXICO</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
@@ -5548,9 +5580,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>revistatendencias@udenar.edu.co</t>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>mcruz@uaem.mx</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
@@ -5560,7 +5592,7 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Angie Vanessa Burbano Erazo.pdf</t>
+          <t>certificados/asistentes/certificado - Marco Antonio Cruz Chávez.pdf</t>
         </is>
       </c>
     </row>
@@ -5572,22 +5604,22 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Marco Antonio Cruz Chávez</t>
+          <t>Francisco Javier Mejía Ochoa</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>INE IDMEX2839443344</t>
+          <t>INE IDMEX1824114106</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD AUTÓNOMA DEL ESTADO DE MORELOS</t>
+          <t>Tecnológico Nacional de México, Instituto Tecnológico Superior de Zongolica</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>CUERNAVACA, MORELOS, MÉXICO</t>
+          <t>Nogales, Veracruz, México</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -5600,9 +5632,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>mcruz@uaem.mx</t>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>francisco_javier_mejia_125@zongolica.tecnm.mx</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
@@ -5612,7 +5644,7 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Marco Antonio Cruz Chávez.pdf</t>
+          <t>certificados/asistentes/certificado - Francisco Javier Mejía Ochoa.pdf</t>
         </is>
       </c>
     </row>
@@ -5624,22 +5656,22 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Francisco Javier Mejía Ochoa</t>
+          <t>Alaín García Peñaloza</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>INE IDMEX1824114106</t>
+          <t>CURP GRPLAL84090315H000</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Tecnológico Nacional de México, Instituto Tecnológico Superior de Zongolica</t>
+          <t>Universidad Autónoma del Estado de México</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Nogales, Veracruz, México</t>
+          <t>Mexico/Toluca</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
@@ -5652,9 +5684,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>francisco_javier_mejia_125@zongolica.tecnm.mx</t>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>algarciape@uaemex.mx</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
@@ -5664,7 +5696,7 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Francisco Javier Mejía Ochoa.pdf</t>
+          <t>certificados/asistentes/certificado - Alaín García Peñaloza.pdf</t>
         </is>
       </c>
     </row>
@@ -5676,22 +5708,22 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Alaín García Peñaloza</t>
+          <t>Bayron Steven López Jáuregui</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>CURP GRPLAL84090315H000</t>
+          <t>C.C. 1.094.044.222</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Universidad Autónoma del Estado de México</t>
+          <t>UNIVERSIDAD FRANCISCO DE PAULA SANTANDER</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Mexico/Toluca</t>
+          <t>COLOMBIA-CUCTA</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -5704,9 +5736,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>algarciape@uaemex.mx</t>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>bayronstevenlj@ufps.edu.co</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
@@ -5716,7 +5748,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Alaín García Peñaloza.pdf</t>
+          <t>certificados/asistentes/certificado - Bayron Steven López Jáuregui.pdf</t>
         </is>
       </c>
     </row>
@@ -5728,22 +5760,22 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Bayron Steven López Jáuregui</t>
+          <t>Emma Elizabeth Paniagua Roldán</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>C.C. 1.094.044.222</t>
+          <t>Pasaporte G41006224</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD FRANCISCO DE PAULA SANTANDER</t>
+          <t>Universidad Nacional Autónoma de México</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>COLOMBIA-CUCTA</t>
+          <t>Ciudad de México, México</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -5756,9 +5788,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>bayronstevenlj@ufps.edu.co</t>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>eepaniaguar@gmail.com</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
@@ -5768,7 +5800,7 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Bayron Steven López Jáuregui.pdf</t>
+          <t>certificados/asistentes/certificado - Emma Elizabeth Paniagua Roldán.pdf</t>
         </is>
       </c>
     </row>
@@ -5780,22 +5812,22 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Emma Elizabeth Paniagua Roldán</t>
+          <t>Mariana Izaguirre Campos</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Pasaporte G41006224</t>
+          <t>INE 2445987847</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Universidad Nacional Autónoma de México</t>
+          <t>Universidad Autónoma de Nuevo León</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Ciudad de México, México</t>
+          <t>México, San Nicolás</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -5808,9 +5840,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>eepaniaguar@gmail.com</t>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>mariana.izaguirrecmp@uanl.edu.mx</t>
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr">
@@ -5820,7 +5852,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Emma Elizabeth Paniagua Roldán.pdf</t>
+          <t>certificados/asistentes/certificado - Mariana Izaguirre Campos.pdf</t>
         </is>
       </c>
     </row>
@@ -5832,22 +5864,22 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Mariana Izaguirre Campos</t>
+          <t>Wesley Pereira Ricardo</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>INE 2445987847</t>
+          <t>D.I. 63.999.561-5</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Universidad Autónoma de Nuevo León</t>
+          <t>Universidade de São Paulo (USP)</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>México, San Nicolás</t>
+          <t>Brasil, Ribeirão Preto</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -5860,9 +5892,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>mariana.izaguirrecmp@uanl.edu.mx</t>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>wesleypereiraricardo@usp.br</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
@@ -5872,7 +5904,7 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Mariana Izaguirre Campos.pdf</t>
+          <t>certificados/asistentes/certificado - Wesley Pereira Ricardo.pdf</t>
         </is>
       </c>
     </row>
@@ -5884,22 +5916,22 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Wesley Pereira Ricardo</t>
+          <t>Héctor Jesús Pérez Hernández</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>D.I. 63.999.561-5</t>
+          <t>C.I. 2855861016</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Universidade de São Paulo (USP)</t>
+          <t>Escuela Normal Veracruzana</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Brasil, Ribeirão Preto</t>
+          <t>Xalapa, Veracruz, México</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -5912,9 +5944,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>wesleypereiraricardo@usp.br</t>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>perezhdez.benv@gmail.com</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
@@ -5924,7 +5956,7 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Wesley Pereira Ricardo.pdf</t>
+          <t>certificados/asistentes/certificado - Héctor Jesús Pérez Hernández.pdf</t>
         </is>
       </c>
     </row>
@@ -5936,22 +5968,22 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Héctor Jesús Pérez Hernández</t>
+          <t>Daniel Neftali Ramirez Salazar</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>C.I. 2855861016</t>
+          <t>DUI 00707384-2</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Escuela Normal Veracruzana</t>
+          <t>UES</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>Xalapa, Veracruz, México</t>
+          <t>EL SALVADOR</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -5964,9 +5996,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>perezhdez.benv@gmail.com</t>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>daniel.salazar@ues.edu.sv</t>
         </is>
       </c>
       <c r="I92" s="3" t="inlineStr">
@@ -5976,7 +6008,7 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Héctor Jesús Pérez Hernández.pdf</t>
+          <t>certificados/asistentes/certificado - Daniel Neftali Ramirez Salazar.pdf</t>
         </is>
       </c>
     </row>
@@ -5988,22 +6020,22 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Daniel Neftali Ramirez Salazar</t>
+          <t>Isela Abigail Lugo Alcantar</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>DUI 00707384-2</t>
+          <t>INE 2511867693</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>UES</t>
+          <t>Universidad Autónoma de Nuevo León</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>EL SALVADOR</t>
+          <t>México, General Zuazua</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -6016,9 +6048,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>daniel.salazar@ues.edu.sv</t>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>28.iselalugo@gmail.com</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
@@ -6028,7 +6060,7 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Daniel Neftali Ramirez Salazar.pdf</t>
+          <t>certificados/asistentes/certificado - Isela Abigail Lugo Alcantar.pdf</t>
         </is>
       </c>
     </row>
@@ -6040,22 +6072,22 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Isela Abigail Lugo Alcantar</t>
+          <t>Napoleón Ernesto López Espinoza</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>INE 2511867693</t>
+          <t>DUI 01343533-7</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Universidad Autónoma de Nuevo León</t>
+          <t>Universidad de El Salvador</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>México, General Zuazua</t>
+          <t>El Salvador, San Salvador</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -6068,9 +6100,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>28.iselalugo@gmail.com</t>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>napoleon.lopez@ues.edu.sv</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
@@ -6080,7 +6112,7 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Isela Abigail Lugo Alcantar.pdf</t>
+          <t>certificados/asistentes/certificado - Napoleón Ernesto López Espinoza.pdf</t>
         </is>
       </c>
     </row>
@@ -6092,22 +6124,22 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Napoleón Ernesto López Espinoza</t>
+          <t>Ligia Marcela Lazo Majano</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>DUI 01343533-7</t>
+          <t>DUI 01267274-0</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Universidad de El Salvador</t>
+          <t>Universidad de El Salvador (UES)</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>El Salvador, San Salvador</t>
+          <t>El Salvador - San Salvador</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -6120,9 +6152,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>napoleon.lopez@ues.edu.sv</t>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>ligia.lazo@ues.edu.sv</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr">
@@ -6132,7 +6164,7 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Napoleón Ernesto López Espinoza.pdf</t>
+          <t>certificados/asistentes/certificado - Ligia Marcela Lazo Majano.pdf</t>
         </is>
       </c>
     </row>
@@ -6144,22 +6176,22 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Ligia Marcela Lazo Majano</t>
+          <t>Mariela Vanessa Meléndez Ascencio</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>DUI 01267274-0</t>
+          <t>DUI 02300379-2</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Universidad de El Salvador (UES)</t>
+          <t>Universidad de El Salvador</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>El Salvador - San Salvador</t>
+          <t>El Salvador, San Salvador</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
@@ -6172,9 +6204,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>ligia.lazo@ues.edu.sv</t>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>mariela.melendez@ues.edu.sv</t>
         </is>
       </c>
       <c r="I96" s="3" t="inlineStr">
@@ -6184,7 +6216,7 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Ligia Marcela Lazo Majano.pdf</t>
+          <t>certificados/asistentes/certificado - Mariela Vanessa Meléndez Ascencio.pdf</t>
         </is>
       </c>
     </row>
@@ -6196,22 +6228,22 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Mariela Vanessa Meléndez Ascencio</t>
+          <t>Miguel Ángel Méndez Cerino</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>DUI 02300379-2</t>
+          <t>INE 2691962005</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Universidad de El Salvador</t>
+          <t>Universidad Autónoma de Nuevo León</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>El Salvador, San Salvador</t>
+          <t>Mexico, Nuevo León, Monterrey</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -6224,9 +6256,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>mariela.melendez@ues.edu.sv</t>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>micah.oct16@gmail.com</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
@@ -6236,7 +6268,7 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Mariela Vanessa Meléndez Ascencio.pdf</t>
+          <t>certificados/asistentes/certificado - Miguel Ángel Méndez Cerino.pdf</t>
         </is>
       </c>
     </row>
@@ -6248,22 +6280,22 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Miguel Ángel Méndez Cerino</t>
+          <t>Cassandra Durán Cárdenas</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>INE 2691962005</t>
+          <t>Pasaporte N00278176</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Universidad Autónoma de Nuevo León</t>
+          <t>Universidad Nacional Autónoma de México</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>Mexico, Nuevo León, Monterrey</t>
+          <t>México</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -6276,9 +6308,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>micah.oct16@gmail.com</t>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>kurinami@comunidad.unam.mx</t>
         </is>
       </c>
       <c r="I98" s="3" t="inlineStr">
@@ -6288,7 +6320,7 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Miguel Ángel Méndez Cerino.pdf</t>
+          <t>certificados/asistentes/certificado - Cassandra Durán Cárdenas.pdf</t>
         </is>
       </c>
     </row>
@@ -6300,22 +6332,22 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Cassandra Durán Cárdenas</t>
+          <t>Karina Eddmy Madrid Gomez</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Pasaporte N00278176</t>
+          <t>DNI 44944170</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Universidad Nacional Autónoma de México</t>
+          <t>Universidad Nacional de Huancavelica</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Perú</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -6328,9 +6360,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>kurinami@comunidad.unam.mx</t>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>eddmymadridgomez@gmail.com</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
@@ -6340,7 +6372,7 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Cassandra Durán Cárdenas.pdf</t>
+          <t>certificados/asistentes/certificado - Karina Eddmy Madrid Gomez.pdf</t>
         </is>
       </c>
     </row>
@@ -6352,22 +6384,22 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Karina Eddmy Madrid Gomez</t>
+          <t>Javier Jiménez Hernández</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>DNI 44944170</t>
+          <t>D.I. JIHJ761004HMCMRV01</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Universidad Nacional de Huancavelica</t>
+          <t>Universidad Autónoma de Guerrero</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Perú</t>
+          <t>México. Estado de Guerrero. Municipio: Chilpancingo</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
@@ -6380,9 +6412,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>eddmymadridgomez@gmail.com</t>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>investigacion@uagro.mx</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
@@ -6392,7 +6424,7 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Karina Eddmy Madrid Gomez.pdf</t>
+          <t>certificados/asistentes/certificado - Javier Jiménez Hernández.pdf</t>
         </is>
       </c>
     </row>
@@ -6404,22 +6436,22 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Javier Jiménez Hernández</t>
+          <t>Wendolyne Nava González</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>D.I. JIHJ761004HMCMRV01</t>
+          <t>INE N12875845</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Universidad Autónoma de Guerrero</t>
+          <t>Universidad Autónoma de Ciudad Juárez</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>México. Estado de Guerrero. Municipio: Chilpancingo</t>
+          <t>Ciudad Juárez, Chihuahua, México</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -6432,9 +6464,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>investigacion@uagro.mx</t>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>wendolyne.nava@uacj.mx</t>
         </is>
       </c>
       <c r="I101" s="3" t="inlineStr">
@@ -6444,7 +6476,7 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>certificados/asistentes/certificado - Javier Jiménez Hernández.pdf</t>
+          <t>certificados/asistentes/certificado - Wendolyne Nava González.pdf</t>
         </is>
       </c>
     </row>
@@ -6456,22 +6488,22 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Wendolyne Nava González</t>
+          <t>María del Rosario Rodríguez León</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>INE N12875845</t>
+          <t>Credencial UNAM 826091</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Universidad Autónoma de Ciudad Juárez</t>
+          <t>UNAM</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>Ciudad Juárez, Chihuahua, México</t>
+          <t>México,  Ciudad de México</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
@@ -6484,9 +6516,9 @@
           <t>4 horas</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>wendolyne.nava@uacj.mx</t>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>mrrodriguezl@dgb.unam.mx</t>
         </is>
       </c>
       <c r="I102" s="3" t="inlineStr">
@@ -6495,58 +6527,6 @@
         </is>
       </c>
       <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>certificados/asistentes/certificado - Wendolyne Nava González.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>FORO26-ASI-102</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>María del Rosario Rodríguez León</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Credencial UNAM 826091</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>UNAM</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="inlineStr">
-        <is>
-          <t>México,  Ciudad de México</t>
-        </is>
-      </c>
-      <c r="F103" s="3" t="inlineStr">
-        <is>
-          <t>Gestión editorial en tiempos de inteligencia artificial</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>4 horas</t>
-        </is>
-      </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>mrrodriguezl@dgb.unam.mx</t>
-        </is>
-      </c>
-      <c r="I103" s="3" t="inlineStr">
-        <is>
-          <t>https://juannietoval.github.io/certificaci-n-II-foro/?id=FORO26-ASI-102</t>
-        </is>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
         <is>
           <t>certificados/asistentes/certificado - María del Rosario Rodríguez León.pdf</t>
         </is>
